--- a/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260930.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260930.xlsx
@@ -1085,17 +1085,17 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>2357</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>華碩</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>15,523,136</t>
+          <t>7,132,409</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -1129,17 +1129,17 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>2357</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>華碩</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>7,132,409</t>
+          <t>15,523,136</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -1239,17 +1239,17 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>71,168,328</t>
+          <t>2,162,733</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -1261,17 +1261,17 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>2,162,733</t>
+          <t>69,474,271</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -1283,17 +1283,17 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>69,474,271</t>
+          <t>71,168,328</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -1503,17 +1503,17 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>26,317,144</t>
+          <t>10,612,315</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -1525,17 +1525,17 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>10,612,315</t>
+          <t>26,317,144</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
